--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OREGON_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/OREGON_2011.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C107">
@@ -2533,7 +2533,7 @@
         <v>89</v>
       </c>
       <c r="D121">
-        <v>0.009978697163359</v>
+        <v>0.009978697163359002</v>
       </c>
     </row>
     <row r="122">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C589">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C890">
